--- a/SALT/nacl_transport.xlsx
+++ b/SALT/nacl_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE374583-0A5F-4B48-A09C-16F4448A7CDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567A23C0-445A-B34F-AA64-B4900F6D572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="3100" windowWidth="27240" windowHeight="15980" activeTab="2" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
+    <workbookView minimized="1" xWindow="1680" yWindow="980" windowWidth="27240" windowHeight="15980" activeTab="2" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,6 +566,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -573,7 +574,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1059,6 +1059,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1066,7 +1067,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1413,6 +1413,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1420,7 +1421,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1964,6 +1964,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1971,7 +1972,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6649,7 +6649,7 @@
         <v>1709</v>
       </c>
       <c r="F8">
-        <f t="shared" ref="F8:F16" si="1">1/E8</f>
+        <f t="shared" ref="F8:F15" si="1">1/E8</f>
         <v>5.8513750731421885E-4</v>
       </c>
       <c r="G8">

--- a/SALT/nacl_transport.xlsx
+++ b/SALT/nacl_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{567A23C0-445A-B34F-AA64-B4900F6D572F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88E7EF6-85BE-3042-8BB8-845A2EE90A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="1680" yWindow="980" windowWidth="27240" windowHeight="15980" activeTab="2" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
+    <workbookView xWindow="13200" yWindow="500" windowWidth="15600" windowHeight="15880" activeTab="2" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,7 +566,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -574,6 +573,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1059,7 +1059,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1067,6 +1066,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1413,7 +1413,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1421,6 +1420,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1964,7 +1964,6 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1972,6 +1971,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>

--- a/SALT/nacl_transport.xlsx
+++ b/SALT/nacl_transport.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beelbw/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/benjaminbeeler/projects/spreadsheets/SALT/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F88E7EF6-85BE-3042-8BB8-845A2EE90A5B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C21E34B-46F0-FB40-99DC-786337DE19EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="13200" yWindow="500" windowWidth="15600" windowHeight="15880" activeTab="2" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
+    <workbookView xWindow="13200" yWindow="500" windowWidth="21020" windowHeight="17420" activeTab="1" xr2:uid="{89D37278-9B58-8249-BAF7-69A5BF39A451}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -566,6 +566,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -573,7 +574,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1059,6 +1059,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1066,7 +1067,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1413,6 +1413,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1420,7 +1421,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1964,6 +1964,7 @@
     </c:plotArea>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1971,7 +1972,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -6575,7 +6575,7 @@
         <v>1150</v>
       </c>
       <c r="P5">
-        <f t="shared" ref="P5:P8" si="0">0.089272*EXP(21960/8.3144/O5)</f>
+        <f t="shared" ref="P5:P12" si="0">0.089272*EXP(21960/8.3144/O5)</f>
         <v>0.88747845399975311</v>
       </c>
     </row>
@@ -6685,6 +6685,13 @@
         <f t="shared" si="2"/>
         <v>1.2142391395415761</v>
       </c>
+      <c r="O9">
+        <v>1350</v>
+      </c>
+      <c r="P9">
+        <f t="shared" si="0"/>
+        <v>0.63152209671737303</v>
+      </c>
     </row>
     <row r="10" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B10">
@@ -6707,6 +6714,13 @@
         <f t="shared" si="2"/>
         <v>0.61221241321889042</v>
       </c>
+      <c r="O10">
+        <v>1400</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>0.58890206398973333</v>
+      </c>
     </row>
     <row r="11" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B11">
@@ -6729,6 +6743,13 @@
         <f t="shared" si="2"/>
         <v>0.93851770513650734</v>
       </c>
+      <c r="O11">
+        <v>1450</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>0.55181105039337075</v>
+      </c>
     </row>
     <row r="12" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B12">
@@ -6750,6 +6771,13 @@
       <c r="G12">
         <f t="shared" si="2"/>
         <v>0.74797112831444701</v>
+      </c>
+      <c r="O12">
+        <v>1500</v>
+      </c>
+      <c r="P12">
+        <f t="shared" si="0"/>
+        <v>0.51930346730358967</v>
       </c>
     </row>
     <row r="13" spans="2:16" x14ac:dyDescent="0.2">
